--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -60,7 +61,7 @@
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
     <col min="8" max="8" width="14.7109375" customWidth="true"/>
@@ -651,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>0</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -666,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="0">
-        <v>0</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J16" s="0">
         <v>0</v>
@@ -686,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D17" s="0">
         <v>0</v>
@@ -721,28 +722,28 @@
         <v>0</v>
       </c>
       <c r="B18" s="0">
-        <v>0</v>
+        <v>0.087719298245614197</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>0.0012680860776829556</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>0.0072127521457937766</v>
       </c>
       <c r="E18" s="0">
-        <v>0</v>
+        <v>0.0041767355828037905</v>
       </c>
       <c r="F18" s="0">
-        <v>0</v>
+        <v>0.0054579194411090593</v>
       </c>
       <c r="G18" s="0">
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>0.017042549565415018</v>
       </c>
       <c r="I18" s="0">
-        <v>0</v>
+        <v>0.011916347242358665</v>
       </c>
       <c r="J18" s="0">
         <v>0</v>
@@ -751,36 +752,36 @@
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>0</v>
+        <v>0.0015550648462040898</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0</v>
+        <v>0.014768140198877608</v>
       </c>
       <c r="B19" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>0.015217032932195423</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E19" s="0">
-        <v>0</v>
+        <v>0.0089501476774366696</v>
       </c>
       <c r="F19" s="0">
-        <v>0</v>
+        <v>0.0036386129607393625</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>0.017042549565414972</v>
       </c>
       <c r="I19" s="0">
-        <v>0</v>
+        <v>0.021846636610990827</v>
       </c>
       <c r="J19" s="0">
         <v>0</v>
@@ -789,36 +790,36 @@
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0</v>
+        <v>0.071379344294575112</v>
       </c>
       <c r="B20" s="0">
-        <v>0</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C20" s="0">
-        <v>0</v>
+        <v>0.029165979786707895</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E20" s="0">
-        <v>0</v>
+        <v>0.025060413496822677</v>
       </c>
       <c r="F20" s="0">
-        <v>0</v>
+        <v>0.018193064803696816</v>
       </c>
       <c r="G20" s="0">
-        <v>0</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>0.039765948985968268</v>
       </c>
       <c r="I20" s="0">
-        <v>0</v>
+        <v>0.061567794085519593</v>
       </c>
       <c r="J20" s="0">
         <v>0</v>
@@ -827,3047 +828,3047 @@
         <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0</v>
+        <v>0.11076105149158236</v>
       </c>
       <c r="B21" s="0">
-        <v>0</v>
+        <v>1.4035087719298272</v>
       </c>
       <c r="C21" s="0">
-        <v>0</v>
+        <v>0.11032348875841713</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>0.20436131079749034</v>
       </c>
       <c r="E21" s="0">
-        <v>0</v>
+        <v>0.060861004206569529</v>
       </c>
       <c r="F21" s="0">
-        <v>0</v>
+        <v>0.045482662009242163</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>0.24140012070006081</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>0.073851048116798407</v>
       </c>
       <c r="I21" s="0">
-        <v>0</v>
+        <v>0.18271732438283286</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>0.036805299963194767</v>
       </c>
       <c r="K21" s="0">
         <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>0.0093303890772245372</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0</v>
+        <v>0.30520823077680392</v>
       </c>
       <c r="B22" s="0">
-        <v>0</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C22" s="0">
-        <v>0</v>
+        <v>0.21050228889537004</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>0.51691390378188595</v>
       </c>
       <c r="E22" s="0">
-        <v>0</v>
+        <v>0.15453921656373984</v>
       </c>
       <c r="F22" s="0">
-        <v>0</v>
+        <v>0.11461630826328992</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>0.27268079304663956</v>
       </c>
       <c r="I22" s="0">
-        <v>0</v>
+        <v>0.40912792198764636</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K22" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L22" s="0">
-        <v>0</v>
+        <v>0.07464311261779609</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0</v>
+        <v>0.53657576055921985</v>
       </c>
       <c r="B23" s="0">
-        <v>0</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>0.42227266386842299</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>1.0218065539874488</v>
       </c>
       <c r="E23" s="0">
-        <v>0</v>
+        <v>0.29774157940272655</v>
       </c>
       <c r="F23" s="0">
-        <v>0</v>
+        <v>0.2383291489284283</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>0.42038288928023593</v>
       </c>
       <c r="I23" s="0">
-        <v>0</v>
+        <v>0.69909237155170645</v>
       </c>
       <c r="J23" s="0">
-        <v>0</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K23" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L23" s="0">
-        <v>0</v>
+        <v>0.15084129008179628</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0</v>
+        <v>0.95992911292704708</v>
       </c>
       <c r="B24" s="0">
-        <v>0</v>
+        <v>4.6491228070175525</v>
       </c>
       <c r="C24" s="0">
-        <v>0</v>
+        <v>0.89907302907721554</v>
       </c>
       <c r="D24" s="0">
-        <v>0</v>
+        <v>1.6252734835188645</v>
       </c>
       <c r="E24" s="0">
-        <v>0</v>
+        <v>0.61219010113666994</v>
       </c>
       <c r="F24" s="0">
-        <v>0</v>
+        <v>0.53669541170905755</v>
       </c>
       <c r="G24" s="0">
-        <v>0</v>
+        <v>0.94548380607523808</v>
       </c>
       <c r="H24" s="0">
-        <v>0</v>
+        <v>1.0168721240697627</v>
       </c>
       <c r="I24" s="0">
-        <v>0</v>
+        <v>1.2889515600484622</v>
       </c>
       <c r="J24" s="0">
-        <v>0</v>
+        <v>0.40485829959514247</v>
       </c>
       <c r="K24" s="0">
-        <v>0</v>
+        <v>0.77319587628866127</v>
       </c>
       <c r="L24" s="0">
-        <v>0</v>
+        <v>0.36855036855036927</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0</v>
+        <v>1.5777296445800912</v>
       </c>
       <c r="B25" s="0">
-        <v>0</v>
+        <v>6.8421052631578894</v>
       </c>
       <c r="C25" s="0">
-        <v>0</v>
+        <v>1.4976096577435665</v>
       </c>
       <c r="D25" s="0">
-        <v>0</v>
+        <v>2.7600798211237443</v>
       </c>
       <c r="E25" s="0">
-        <v>0</v>
+        <v>1.0227035412750967</v>
       </c>
       <c r="F25" s="0">
-        <v>0</v>
+        <v>0.96969035403704029</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>2.051901025950511</v>
       </c>
       <c r="H25" s="0">
-        <v>0</v>
+        <v>1.6190422087144221</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>2.1171376933923836</v>
       </c>
       <c r="J25" s="0">
-        <v>0</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K25" s="0">
-        <v>0</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L25" s="0">
-        <v>0</v>
+        <v>0.58625944701894017</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0</v>
+        <v>2.385054642118734</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>6.3157894736842053</v>
       </c>
       <c r="C26" s="0">
-        <v>0</v>
+        <v>2.2584613043533377</v>
       </c>
       <c r="D26" s="0">
-        <v>0</v>
+        <v>3.8900776572980993</v>
       </c>
       <c r="E26" s="0">
-        <v>0</v>
+        <v>1.5871595214654362</v>
       </c>
       <c r="F26" s="0">
-        <v>0</v>
+        <v>1.548229814794599</v>
       </c>
       <c r="G26" s="0">
-        <v>0</v>
+        <v>2.5950512975256466</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>2.2609782423450526</v>
       </c>
       <c r="I26" s="0">
-        <v>0</v>
+        <v>2.8341045858076277</v>
       </c>
       <c r="J26" s="0">
-        <v>0</v>
+        <v>1.8770702981229279</v>
       </c>
       <c r="K26" s="0">
-        <v>0</v>
+        <v>2.9639175257731933</v>
       </c>
       <c r="L26" s="0">
-        <v>0</v>
+        <v>1.1196466892669414</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0</v>
+        <v>2.8084079944865588</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>7.5438596491228003</v>
       </c>
       <c r="C27" s="0">
-        <v>0</v>
+        <v>3.0307257256622551</v>
       </c>
       <c r="D27" s="0">
-        <v>0.002404250715264586</v>
+        <v>4.7532036640780859</v>
       </c>
       <c r="E27" s="0">
-        <v>0.0005966765118291113</v>
+        <v>2.2387302723828255</v>
       </c>
       <c r="F27" s="0">
-        <v>0</v>
+        <v>2.4578830549794395</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>3.7819352243009421</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>3.0335738226438647</v>
       </c>
       <c r="I27" s="0">
-        <v>0</v>
+        <v>3.6424301404142887</v>
       </c>
       <c r="J27" s="0">
-        <v>0</v>
+        <v>2.9444239970555737</v>
       </c>
       <c r="K27" s="0">
-        <v>0</v>
+        <v>5.4123711340206135</v>
       </c>
       <c r="L27" s="0">
-        <v>0</v>
+        <v>1.8598575560600861</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0</v>
+        <v>3.4778970168356769</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>6.6666666666666608</v>
       </c>
       <c r="C28" s="0">
-        <v>0</v>
+        <v>3.6520879037269016</v>
       </c>
       <c r="D28" s="0">
-        <v>0</v>
+        <v>5.6379679272954535</v>
       </c>
       <c r="E28" s="0">
-        <v>0.0011933530236582226</v>
+        <v>2.878964169575462</v>
       </c>
       <c r="F28" s="0">
-        <v>0</v>
+        <v>3.0673507259032831</v>
       </c>
       <c r="G28" s="0">
-        <v>0</v>
+        <v>4.304968819151072</v>
       </c>
       <c r="H28" s="0">
-        <v>0.005680849855138323</v>
+        <v>4.0106799977276566</v>
       </c>
       <c r="I28" s="0">
-        <v>0</v>
+        <v>4.4368532899048638</v>
       </c>
       <c r="J28" s="0">
-        <v>0</v>
+        <v>3.6805299963194664</v>
       </c>
       <c r="K28" s="0">
-        <v>0</v>
+        <v>9.4072164948453523</v>
       </c>
       <c r="L28" s="0">
-        <v>0</v>
+        <v>2.5518614126209038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0</v>
+        <v>3.7904893177119408</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>5.438596491228096</v>
       </c>
       <c r="C29" s="0">
-        <v>0.0038042582330488767</v>
+        <v>4.3330501274426716</v>
       </c>
       <c r="D29" s="0">
-        <v>0.002404250715264599</v>
+        <v>5.8471377395235047</v>
       </c>
       <c r="E29" s="0">
-        <v>0.0077567946537784897</v>
+        <v>3.4123929711507066</v>
       </c>
       <c r="F29" s="0">
-        <v>0.0018193064803696914</v>
+        <v>3.7495906560419341</v>
       </c>
       <c r="G29" s="0">
-        <v>0</v>
+        <v>5.3510360088513629</v>
       </c>
       <c r="H29" s="0">
-        <v>0.01136169971027671</v>
+        <v>4.4708288359938857</v>
       </c>
       <c r="I29" s="0">
-        <v>0.0039721157474528991</v>
+        <v>4.6136124406665422</v>
       </c>
       <c r="J29" s="0">
-        <v>0</v>
+        <v>4.5638571954361638</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>8.3762886597938522</v>
       </c>
       <c r="L29" s="0">
-        <v>0.0015550648462040941</v>
+        <v>3.4506888937268845</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0024613566998129346</v>
+        <v>3.9972432804962055</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>4.122807017543856</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0088766025437806654</v>
+        <v>4.651339732941068</v>
       </c>
       <c r="D30" s="0">
-        <v>0.004808501430529172</v>
+        <v>5.5946914144206907</v>
       </c>
       <c r="E30" s="0">
-        <v>0.019690324890360673</v>
+        <v>3.8109728810525336</v>
       </c>
       <c r="F30" s="0">
-        <v>0.01273514536258777</v>
+        <v>4.1098133391551102</v>
       </c>
       <c r="G30" s="0">
-        <v>0.080466706900020044</v>
+        <v>5.009052504526248</v>
       </c>
       <c r="H30" s="0">
-        <v>0.022723399420553292</v>
+        <v>4.6071692325171805</v>
       </c>
       <c r="I30" s="0">
-        <v>0.0019860578737264387</v>
+        <v>4.9651446843160967</v>
       </c>
       <c r="J30" s="0">
-        <v>0</v>
+        <v>5.2815605447184346</v>
       </c>
       <c r="K30" s="0">
-        <v>0</v>
+        <v>13.917525773195864</v>
       </c>
       <c r="L30" s="0">
-        <v>0.0015550648462040854</v>
+        <v>3.8752215967405808</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0</v>
+        <v>3.7658757507137906</v>
       </c>
       <c r="B31" s="0">
-        <v>0.17543859649122792</v>
+        <v>3.0701754385964883</v>
       </c>
       <c r="C31" s="0">
-        <v>0.021557463320610183</v>
+        <v>4.704599348203752</v>
       </c>
       <c r="D31" s="0">
-        <v>0.038468011444233376</v>
+        <v>5.0705647584930116</v>
       </c>
       <c r="E31" s="0">
-        <v>0.047734120946328909</v>
+        <v>3.8843640920075147</v>
       </c>
       <c r="F31" s="0">
-        <v>0.027289597205545222</v>
+        <v>4.5064221518757011</v>
       </c>
       <c r="G31" s="0">
-        <v>0.12070006035003007</v>
+        <v>4.2043854355260475</v>
       </c>
       <c r="H31" s="0">
-        <v>0.051127648696244914</v>
+        <v>4.1867863432369452</v>
       </c>
       <c r="I31" s="0">
-        <v>0.0099302893686321926</v>
+        <v>4.8598836170085953</v>
       </c>
       <c r="J31" s="0">
-        <v>0.018402649981597335</v>
+        <v>5.3919764446080185</v>
       </c>
       <c r="K31" s="0">
-        <v>0</v>
+        <v>12.757731958762875</v>
       </c>
       <c r="L31" s="0">
-        <v>0.015550648462040852</v>
+        <v>4.1022610642863766</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.019690853598503477</v>
+        <v>3.6083489219257623</v>
       </c>
       <c r="B32" s="0">
-        <v>0.70175438596491169</v>
+        <v>2.1929824561403488</v>
       </c>
       <c r="C32" s="0">
-        <v>0.073548992505611213</v>
+        <v>4.3812373983945996</v>
       </c>
       <c r="D32" s="0">
-        <v>0.10578703147164176</v>
+        <v>4.1737792416993207</v>
       </c>
       <c r="E32" s="0">
-        <v>0.11456189027118938</v>
+        <v>3.9368716250484761</v>
       </c>
       <c r="F32" s="0">
-        <v>0.078230178655896293</v>
+        <v>4.2862860677509698</v>
       </c>
       <c r="G32" s="0">
-        <v>0.28163347415007012</v>
+        <v>3.6612351639509124</v>
       </c>
       <c r="H32" s="0">
-        <v>0.14202124637845809</v>
+        <v>3.6584673067090807</v>
       </c>
       <c r="I32" s="0">
-        <v>0.029790868105896578</v>
+        <v>4.3931600166828826</v>
       </c>
       <c r="J32" s="0">
-        <v>0.018402649981597335</v>
+        <v>4.4718439455281525</v>
       </c>
       <c r="K32" s="0">
-        <v>0</v>
+        <v>7.8608247422680337</v>
       </c>
       <c r="L32" s="0">
-        <v>0.038876621155102133</v>
+        <v>4.4288246819892345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.093531554592891517</v>
+        <v>3.6624987693216471</v>
       </c>
       <c r="B33" s="0">
-        <v>0.96491228070175361</v>
+        <v>1.4035087719298234</v>
       </c>
       <c r="C33" s="0">
-        <v>0.14456181285585654</v>
+        <v>4.2620373070924016</v>
       </c>
       <c r="D33" s="0">
-        <v>0.25004207438751691</v>
+        <v>3.5294400500084122</v>
       </c>
       <c r="E33" s="0">
-        <v>0.24583072287359384</v>
+        <v>3.7823324084847365</v>
       </c>
       <c r="F33" s="0">
-        <v>0.14918313139031389</v>
+        <v>4.029763854018845</v>
       </c>
       <c r="G33" s="0">
-        <v>0.46268356467511529</v>
+        <v>3.339368336350832</v>
       </c>
       <c r="H33" s="0">
-        <v>0.28404249275691618</v>
+        <v>3.1869567687325997</v>
       </c>
       <c r="I33" s="0">
-        <v>0.05560962046434028</v>
+        <v>4.381243669440523</v>
       </c>
       <c r="J33" s="0">
-        <v>0.11041589988958402</v>
+        <v>4.06698564593301</v>
       </c>
       <c r="K33" s="0">
-        <v>0.38659793814432958</v>
+        <v>6.8298969072164884</v>
       </c>
       <c r="L33" s="0">
-        <v>0.13529064161975543</v>
+        <v>4.1240319721332348</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.15506547208821489</v>
+        <v>3.3056020478487711</v>
       </c>
       <c r="B34" s="0">
-        <v>1.7543859649122791</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C34" s="0">
-        <v>0.33984706881903115</v>
+        <v>3.9133136357295899</v>
       </c>
       <c r="D34" s="0">
-        <v>0.67799870170461318</v>
+        <v>3.0125261462265258</v>
       </c>
       <c r="E34" s="0">
-        <v>0.4803245920224346</v>
+        <v>3.6910409021748825</v>
       </c>
       <c r="F34" s="0">
-        <v>0.33657169886839106</v>
+        <v>3.6804570097878653</v>
       </c>
       <c r="G34" s="0">
-        <v>0.56326694830014024</v>
+        <v>3.0175015087507515</v>
       </c>
       <c r="H34" s="0">
-        <v>0.55672328580355568</v>
+        <v>2.7892972788729171</v>
       </c>
       <c r="I34" s="0">
-        <v>0.1847033822565588</v>
+        <v>4.0475859466544817</v>
       </c>
       <c r="J34" s="0">
-        <v>0.31284504968715471</v>
+        <v>3.6621273463378694</v>
       </c>
       <c r="K34" s="0">
-        <v>0.38659793814432958</v>
+        <v>5.6701030927835001</v>
       </c>
       <c r="L34" s="0">
-        <v>0.27058128323951086</v>
+        <v>3.9483096445121726</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.3372058678743739</v>
+        <v>3.3695973220439264</v>
       </c>
       <c r="B35" s="0">
-        <v>2.3684210526315899</v>
+        <v>0.61403508771930115</v>
       </c>
       <c r="C35" s="0">
-        <v>0.62389835022001583</v>
+        <v>3.7649475646407056</v>
       </c>
       <c r="D35" s="0">
-        <v>1.2069338590628287</v>
+        <v>2.8201860890053747</v>
       </c>
       <c r="E35" s="0">
-        <v>0.91947850472866577</v>
+        <v>3.4863808586175171</v>
       </c>
       <c r="F35" s="0">
-        <v>0.79503693192155522</v>
+        <v>3.6640832514645587</v>
       </c>
       <c r="G35" s="0">
-        <v>1.2874673104003278</v>
+        <v>2.6755180044256814</v>
       </c>
       <c r="H35" s="0">
-        <v>1.0850423223314258</v>
+        <v>2.4541271374197695</v>
       </c>
       <c r="I35" s="0">
-        <v>0.39522551687156343</v>
+        <v>3.9343806478520973</v>
       </c>
       <c r="J35" s="0">
-        <v>0.68089804931910514</v>
+        <v>2.8156054471844079</v>
       </c>
       <c r="K35" s="0">
-        <v>0.77319587628866338</v>
+        <v>4.3814432989690921</v>
       </c>
       <c r="L35" s="0">
-        <v>0.52561191801698381</v>
+        <v>3.77569744658354</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.58826425125529136</v>
+        <v>3.3597518952446559</v>
       </c>
       <c r="B36" s="0">
-        <v>4.122807017543856</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C36" s="0">
-        <v>1.1476179003030715</v>
+        <v>3.4694835085405567</v>
       </c>
       <c r="D36" s="0">
-        <v>1.9522515807948435</v>
+        <v>2.901930613324355</v>
       </c>
       <c r="E36" s="0">
-        <v>1.431426951878038</v>
+        <v>3.4571437095378714</v>
       </c>
       <c r="F36" s="0">
-        <v>1.182549212240293</v>
+        <v>3.4785139904668307</v>
       </c>
       <c r="G36" s="0">
-        <v>2.4341178837256066</v>
+        <v>2.6151679742506517</v>
       </c>
       <c r="H36" s="0">
-        <v>1.8633187524853703</v>
+        <v>2.5507015849571073</v>
       </c>
       <c r="I36" s="0">
-        <v>0.75072987626859378</v>
+        <v>3.5431272467279662</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0673536989326453</v>
+        <v>2.3555391976444589</v>
       </c>
       <c r="K36" s="0">
-        <v>1.2886597938144317</v>
+        <v>2.3195876288659774</v>
       </c>
       <c r="L36" s="0">
-        <v>0.94703449133828799</v>
+        <v>3.6310764158865392</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>1.050999310820123</v>
+        <v>3.1874569262577506</v>
       </c>
       <c r="B37" s="0">
-        <v>5.7017543859649065</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C37" s="0">
-        <v>1.8894482557475982</v>
+        <v>3.4111515489671409</v>
       </c>
       <c r="D37" s="0">
-        <v>3.0125261462265258</v>
+        <v>3.2120789555934866</v>
       </c>
       <c r="E37" s="0">
-        <v>2.0263134341716622</v>
+        <v>3.1635788657179482</v>
       </c>
       <c r="F37" s="0">
-        <v>1.9066331914274264</v>
+        <v>3.1201106138340036</v>
       </c>
       <c r="G37" s="0">
-        <v>2.8968014484007214</v>
+        <v>2.5145845906256263</v>
       </c>
       <c r="H37" s="0">
-        <v>2.6302334829290439</v>
+        <v>2.6643185820598738</v>
       </c>
       <c r="I37" s="0">
-        <v>1.3247006017755345</v>
+        <v>3.3504796329765023</v>
       </c>
       <c r="J37" s="0">
-        <v>2.3923444976076533</v>
+        <v>2.2451232977548745</v>
       </c>
       <c r="K37" s="0">
-        <v>2.7061855670103068</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L37" s="0">
-        <v>1.5395141977420443</v>
+        <v>3.5128914875750286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>1.7254110465688672</v>
+        <v>2.9856256768730898</v>
       </c>
       <c r="B38" s="0">
-        <v>5.350877192982451</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C38" s="0">
-        <v>2.7187765505522492</v>
+        <v>3.1854322271395756</v>
       </c>
       <c r="D38" s="0">
-        <v>4.1473324838314101</v>
+        <v>3.5462698050152635</v>
       </c>
       <c r="E38" s="0">
-        <v>2.7554521316268361</v>
+        <v>3.1647722187416063</v>
       </c>
       <c r="F38" s="0">
-        <v>2.6816577520649107</v>
+        <v>3.0564348870210649</v>
       </c>
       <c r="G38" s="0">
-        <v>4.043452021726007</v>
+        <v>3.1583182458257868</v>
       </c>
       <c r="H38" s="0">
-        <v>3.3630631142418874</v>
+        <v>3.0676589217746946</v>
       </c>
       <c r="I38" s="0">
-        <v>2.1707612559829972</v>
+        <v>3.1359853826140469</v>
       </c>
       <c r="J38" s="0">
-        <v>2.8340080971659893</v>
+        <v>2.0794994479204987</v>
       </c>
       <c r="K38" s="0">
-        <v>5.2835051546391707</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L38" s="0">
-        <v>2.2579541566883319</v>
+        <v>3.4320281155724159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>2.4761248400118125</v>
+        <v>2.9437826129762699</v>
       </c>
       <c r="B39" s="0">
-        <v>6.4912280701754321</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C39" s="0">
-        <v>3.3972026021126283</v>
+        <v>2.8823596545733499</v>
       </c>
       <c r="D39" s="0">
-        <v>5.1138412713677743</v>
+        <v>3.476546534272591</v>
       </c>
       <c r="E39" s="0">
-        <v>3.2805274620364537</v>
+        <v>3.034100062651031</v>
       </c>
       <c r="F39" s="0">
-        <v>3.4166575701342619</v>
+        <v>2.9399992722774053</v>
       </c>
       <c r="G39" s="0">
-        <v>5.069402534701263</v>
+        <v>2.6554013277006616</v>
       </c>
       <c r="H39" s="0">
-        <v>4.2038288928023597</v>
+        <v>2.9426802249616517</v>
       </c>
       <c r="I39" s="0">
-        <v>2.7923973704593728</v>
+        <v>2.9651844054735728</v>
       </c>
       <c r="J39" s="0">
-        <v>4.1221935958778024</v>
+        <v>2.4843577475156402</v>
       </c>
       <c r="K39" s="0">
-        <v>8.7628865979381363</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L39" s="0">
-        <v>3.0945790439461298</v>
+        <v>3.3496096787236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.0693118046667296</v>
+        <v>2.6558038790981566</v>
       </c>
       <c r="B40" s="0">
-        <v>8.5087719298245545</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C40" s="0">
-        <v>4.0984542030713005</v>
+        <v>2.8316362114660318</v>
       </c>
       <c r="D40" s="0">
-        <v>5.8014569759334451</v>
+        <v>3.358738249224626</v>
       </c>
       <c r="E40" s="0">
-        <v>3.6606104000715978</v>
+        <v>2.9195381723798417</v>
       </c>
       <c r="F40" s="0">
-        <v>3.9133282392751849</v>
+        <v>2.805370592730049</v>
       </c>
       <c r="G40" s="0">
-        <v>5.069402534701263</v>
+        <v>2.9772681553007416</v>
       </c>
       <c r="H40" s="0">
-        <v>4.6242117820825959</v>
+        <v>2.9881270238027584</v>
       </c>
       <c r="I40" s="0">
-        <v>3.499433973505985</v>
+        <v>2.8043137177017314</v>
       </c>
       <c r="J40" s="0">
-        <v>4.913507545086488</v>
+        <v>2.7788001472211974</v>
       </c>
       <c r="K40" s="0">
-        <v>8.7628865979381363</v>
+        <v>0</v>
       </c>
       <c r="L40" s="0">
-        <v>3.7383758902746207</v>
+        <v>3.0012751531738844</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.6649601260214801</v>
+        <v>2.6139608152013514</v>
       </c>
       <c r="B41" s="0">
-        <v>5.9649122807017818</v>
+        <v>1.0526315789473733</v>
       </c>
       <c r="C41" s="0">
-        <v>4.3901140009384045</v>
+        <v>2.7048276036977517</v>
       </c>
       <c r="D41" s="0">
-        <v>5.8856057509677386</v>
+        <v>3.0221431490876007</v>
       </c>
       <c r="E41" s="0">
-        <v>3.8801873564247322</v>
+        <v>2.8276499895581741</v>
       </c>
       <c r="F41" s="0">
-        <v>4.3263108103191259</v>
+        <v>2.5925117345268105</v>
       </c>
       <c r="G41" s="0">
-        <v>4.8280024140012294</v>
+        <v>2.454234560450625</v>
       </c>
       <c r="H41" s="0">
-        <v>4.5730841333863763</v>
+        <v>2.9483610748168063</v>
       </c>
       <c r="I41" s="0">
-        <v>4.4090484796727178</v>
+        <v>2.5262656153800438</v>
       </c>
       <c r="J41" s="0">
-        <v>5.2815605447184639</v>
+        <v>3.1100478468899664</v>
       </c>
       <c r="K41" s="0">
-        <v>12.371134020618614</v>
+        <v>0</v>
       </c>
       <c r="L41" s="0">
-        <v>4.100705999440196</v>
+        <v>2.8504338630921042</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.7978733878113582</v>
+        <v>2.6754947326966603</v>
       </c>
       <c r="B42" s="0">
-        <v>4.122807017543856</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C42" s="0">
-        <v>4.6589482494071657</v>
+        <v>2.5818232541624902</v>
       </c>
       <c r="D42" s="0">
-        <v>5.5033298872406364</v>
+        <v>2.639867285360515</v>
       </c>
       <c r="E42" s="0">
-        <v>3.9404516841194508</v>
+        <v>2.6540171246158875</v>
       </c>
       <c r="F42" s="0">
-        <v>4.300840519593927</v>
+        <v>2.6761998326238015</v>
       </c>
       <c r="G42" s="0">
-        <v>3.822168577750952</v>
+        <v>2.4542345604506113</v>
       </c>
       <c r="H42" s="0">
-        <v>4.0788501959893164</v>
+        <v>2.652956882349597</v>
       </c>
       <c r="I42" s="0">
-        <v>4.9214514110941154</v>
+        <v>2.4925026315266803</v>
       </c>
       <c r="J42" s="0">
-        <v>4.9319101950680855</v>
+        <v>2.5763709974236271</v>
       </c>
       <c r="K42" s="0">
-        <v>12.757731958762875</v>
+        <v>0</v>
       </c>
       <c r="L42" s="0">
-        <v>4.3588467639100514</v>
+        <v>2.7757907504742922</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.8889435857044368</v>
+        <v>2.5425814709067618</v>
       </c>
       <c r="B43" s="0">
-        <v>4.736842105263154</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C43" s="0">
-        <v>4.4053310338705751</v>
+        <v>2.4055592893645597</v>
       </c>
       <c r="D43" s="0">
-        <v>4.7339696583559689</v>
+        <v>2.1566128915923333</v>
       </c>
       <c r="E43" s="0">
-        <v>3.8610937080461794</v>
+        <v>2.6373101822846721</v>
       </c>
       <c r="F43" s="0">
-        <v>4.208055889095073</v>
+        <v>2.405123167048719</v>
       </c>
       <c r="G43" s="0">
-        <v>3.6008851337758969</v>
+        <v>2.1927177630255463</v>
       </c>
       <c r="H43" s="0">
-        <v>3.5618928591717292</v>
+        <v>2.4143611884337877</v>
       </c>
       <c r="I43" s="0">
-        <v>4.9035768902305774</v>
+        <v>2.2780083811642249</v>
       </c>
       <c r="J43" s="0">
-        <v>4.5822598454177363</v>
+        <v>2.9812292970187682</v>
       </c>
       <c r="K43" s="0">
-        <v>8.5051546391752506</v>
+        <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>4.2173358629054789</v>
+        <v>2.5876279040835981</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.7560303239145383</v>
+        <v>2.4785861967116252</v>
       </c>
       <c r="B44" s="0">
-        <v>2.5438596491228047</v>
+        <v>2.6315789473684186</v>
       </c>
       <c r="C44" s="0">
-        <v>4.3647522793847209</v>
+        <v>2.3611762766456566</v>
       </c>
       <c r="D44" s="0">
-        <v>3.9934604380544769</v>
+        <v>1.8416560478926727</v>
       </c>
       <c r="E44" s="0">
-        <v>3.7745756138309581</v>
+        <v>2.5543721471404255</v>
       </c>
       <c r="F44" s="0">
-        <v>3.9042317068733365</v>
+        <v>2.2413855838154477</v>
       </c>
       <c r="G44" s="0">
-        <v>3.3796016898008419</v>
+        <v>1.8507342587004612</v>
       </c>
       <c r="H44" s="0">
-        <v>2.9824461739476202</v>
+        <v>2.0735101971254881</v>
       </c>
       <c r="I44" s="0">
-        <v>4.8281066910289718</v>
+        <v>2.1906218347202615</v>
       </c>
       <c r="J44" s="0">
-        <v>3.993375046006622</v>
+        <v>2.5579683474420296</v>
       </c>
       <c r="K44" s="0">
-        <v>7.2164948453608178</v>
+        <v>0</v>
       </c>
       <c r="L44" s="0">
-        <v>4.1115914533636015</v>
+        <v>2.4103505116163322</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>3.5812739982278203</v>
+        <v>2.4638180565127477</v>
       </c>
       <c r="B45" s="0">
-        <v>1.5789473684210513</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C45" s="0">
-        <v>4.2328713273056939</v>
+        <v>2.2622655625863866</v>
       </c>
       <c r="D45" s="0">
-        <v>3.19284494987137</v>
+        <v>1.5747842184983036</v>
       </c>
       <c r="E45" s="0">
-        <v>3.5096512425788329</v>
+        <v>2.4600972582714258</v>
       </c>
       <c r="F45" s="0">
-        <v>3.6677218644252774</v>
+        <v>2.2322890514135994</v>
       </c>
       <c r="G45" s="0">
-        <v>2.2128344397505515</v>
+        <v>2.051901025950511</v>
       </c>
       <c r="H45" s="0">
-        <v>2.6359143327841821</v>
+        <v>1.6872124069760819</v>
       </c>
       <c r="I45" s="0">
-        <v>4.5004071418641098</v>
+        <v>2.0178347997060615</v>
       </c>
       <c r="J45" s="0">
-        <v>3.4044902465955067</v>
+        <v>1.5090172984909813</v>
       </c>
       <c r="K45" s="0">
-        <v>6.1855670103092733</v>
+        <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>3.8332348458930703</v>
+        <v>2.2284079246104542</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>3.4877424436349282</v>
+        <v>2.2078369597322025</v>
       </c>
       <c r="B46" s="0">
-        <v>1.4912280701754372</v>
+        <v>3.5087719298245581</v>
       </c>
       <c r="C46" s="0">
-        <v>3.8701987090883696</v>
+        <v>2.0073802609721128</v>
       </c>
       <c r="D46" s="0">
-        <v>2.9668453826364987</v>
+        <v>1.7406775178515599</v>
       </c>
       <c r="E46" s="0">
-        <v>3.4434201497658012</v>
+        <v>2.3688057519615722</v>
       </c>
       <c r="F46" s="0">
-        <v>3.5803951533675331</v>
+        <v>2.1831677764436175</v>
       </c>
       <c r="G46" s="0">
-        <v>2.5749346208006414</v>
+        <v>2.0116676725005012</v>
       </c>
       <c r="H46" s="0">
-        <v>2.1928080440833928</v>
+        <v>1.9258081008918917</v>
       </c>
       <c r="I46" s="0">
-        <v>4.4467835792734958</v>
+        <v>1.9622251792417211</v>
       </c>
       <c r="J46" s="0">
-        <v>2.7788001472211974</v>
+        <v>1.821862348178136</v>
       </c>
       <c r="K46" s="0">
-        <v>4.3814432989690681</v>
+        <v>0</v>
       </c>
       <c r="L46" s="0">
-        <v>3.7150499175815597</v>
+        <v>2.1382141635306176</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>3.3622132519444872</v>
+        <v>2.1069213350398841</v>
       </c>
       <c r="B47" s="0">
-        <v>0.26315789473684331</v>
+        <v>3.5964912280701924</v>
       </c>
       <c r="C47" s="0">
-        <v>3.8093305773596087</v>
+        <v>1.9921632280399289</v>
       </c>
       <c r="D47" s="0">
-        <v>2.8298030918664332</v>
+        <v>1.7839540307263324</v>
       </c>
       <c r="E47" s="0">
-        <v>3.2668039022644026</v>
+        <v>2.2560338912258824</v>
       </c>
       <c r="F47" s="0">
-        <v>3.3165957137139479</v>
+        <v>2.0358039515336848</v>
       </c>
       <c r="G47" s="0">
-        <v>2.6352846509756711</v>
+        <v>2.1726010863005532</v>
       </c>
       <c r="H47" s="0">
-        <v>2.6472760324944735</v>
+        <v>1.7440209055274749</v>
       </c>
       <c r="I47" s="0">
-        <v>4.0833349883815808</v>
+        <v>1.8668944013028628</v>
       </c>
       <c r="J47" s="0">
-        <v>2.2635259477364844</v>
+        <v>1.9690835480309257</v>
       </c>
       <c r="K47" s="0">
-        <v>2.1907216494845461</v>
+        <v>0.1288659793814439</v>
       </c>
       <c r="L47" s="0">
-        <v>3.4802351258047621</v>
+        <v>2.0760115696824655</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>3.4114403859407272</v>
+        <v>2.1610711824357569</v>
       </c>
       <c r="B48" s="0">
-        <v>0.87719298245613953</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C48" s="0">
-        <v>3.4352451844431169</v>
+        <v>1.8793035671261349</v>
       </c>
       <c r="D48" s="0">
-        <v>3.0077176447959966</v>
+        <v>1.7478902699973538</v>
       </c>
       <c r="E48" s="0">
-        <v>3.1540320415286822</v>
+        <v>2.2130731823741741</v>
       </c>
       <c r="F48" s="0">
-        <v>3.1910635665684217</v>
+        <v>1.9466579339955592</v>
       </c>
       <c r="G48" s="0">
-        <v>3.2589016294508117</v>
+        <v>1.7702675518004409</v>
       </c>
       <c r="H48" s="0">
-        <v>2.5904675339430754</v>
+        <v>1.8292336533545404</v>
       </c>
       <c r="I48" s="0">
-        <v>3.7318027447319784</v>
+        <v>1.7378006395106336</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4107471475892508</v>
+        <v>1.6194331983805654</v>
       </c>
       <c r="K48" s="0">
-        <v>1.6752577319587614</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L48" s="0">
-        <v>3.363605262339437</v>
+        <v>1.8443069075980452</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>3.261297627252139</v>
+        <v>1.9567785763512831</v>
       </c>
       <c r="B49" s="0">
-        <v>0.43859649122806976</v>
+        <v>1.8421052631578929</v>
       </c>
       <c r="C49" s="0">
-        <v>3.1803598828288431</v>
+        <v>1.8032184024651576</v>
       </c>
       <c r="D49" s="0">
-        <v>3.1760151948645174</v>
+        <v>1.7118265092683849</v>
       </c>
       <c r="E49" s="0">
-        <v>3.0830275366210182</v>
+        <v>2.14863211909663</v>
       </c>
       <c r="F49" s="0">
-        <v>3.0127715314921928</v>
+        <v>1.8884401266237296</v>
       </c>
       <c r="G49" s="0">
-        <v>3.5003017501508715</v>
+        <v>2.1726010863005412</v>
       </c>
       <c r="H49" s="0">
-        <v>2.9256376753962368</v>
+        <v>2.050786797704935</v>
       </c>
       <c r="I49" s="0">
-        <v>3.4497825266628239</v>
+        <v>1.5570693730015279</v>
       </c>
       <c r="J49" s="0">
-        <v>2.3923444976076533</v>
+        <v>1.6378358483621627</v>
       </c>
       <c r="K49" s="0">
         <v>0.38659793814432958</v>
       </c>
       <c r="L49" s="0">
-        <v>3.2967374739526605</v>
+        <v>1.9484962522937188</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>3.1505365757605563</v>
+        <v>1.9149355124544631</v>
       </c>
       <c r="B50" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C50" s="0">
-        <v>2.9774661103995714</v>
+        <v>1.7043076884058874</v>
       </c>
       <c r="D50" s="0">
-        <v>3.4837592864183846</v>
+        <v>1.6012309763662138</v>
       </c>
       <c r="E50" s="0">
-        <v>2.9559354396014172</v>
+        <v>2.1038813807094465</v>
       </c>
       <c r="F50" s="0">
-        <v>2.8144671251318973</v>
+        <v>1.7956554961248756</v>
       </c>
       <c r="G50" s="0">
-        <v>2.8968014484007214</v>
+        <v>1.9312009656004812</v>
       </c>
       <c r="H50" s="0">
-        <v>2.9369993751065131</v>
+        <v>2.0053399988638283</v>
       </c>
       <c r="I50" s="0">
-        <v>3.3842426168298512</v>
+        <v>1.3544914698814312</v>
       </c>
       <c r="J50" s="0">
-        <v>2.5027603974972377</v>
+        <v>1.8770702981229279</v>
       </c>
       <c r="K50" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L50" s="0">
-        <v>3.0883587845613136</v>
+        <v>1.7743289895188614</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.975780250073838</v>
+        <v>1.816481244461946</v>
       </c>
       <c r="B51" s="0">
-        <v>0.35087719298245584</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C51" s="0">
-        <v>2.8481213304759101</v>
+        <v>1.614273576890398</v>
       </c>
       <c r="D51" s="0">
-        <v>3.5751208135984385</v>
+        <v>1.5242949534777472</v>
       </c>
       <c r="E51" s="0">
-        <v>2.824666606999013</v>
+        <v>1.9445687520510739</v>
       </c>
       <c r="F51" s="0">
-        <v>2.809009205690788</v>
+        <v>1.6464723647345618</v>
       </c>
       <c r="G51" s="0">
-        <v>2.9169181251257266</v>
+        <v>1.7501508750754358</v>
       </c>
       <c r="H51" s="0">
-        <v>3.2096801681531528</v>
+        <v>2.0735101971254881</v>
       </c>
       <c r="I51" s="0">
-        <v>3.1220829774979615</v>
+        <v>1.4140732060932242</v>
       </c>
       <c r="J51" s="0">
-        <v>2.7788001472211974</v>
+        <v>1.6746411483253574</v>
       </c>
       <c r="K51" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L51" s="0">
-        <v>2.8504338630920882</v>
+        <v>1.8147606755201677</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.8379442748843138</v>
+        <v>1.4694299497883221</v>
       </c>
       <c r="B52" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C52" s="0">
-        <v>2.8493894165535929</v>
+        <v>1.4392776981701505</v>
       </c>
       <c r="D52" s="0">
-        <v>3.2048662034476925</v>
+        <v>1.2357848676459971</v>
       </c>
       <c r="E52" s="0">
-        <v>2.7303917181300137</v>
+        <v>1.8705808645842641</v>
       </c>
       <c r="F52" s="0">
-        <v>2.6398137030164079</v>
+        <v>1.5991703962449502</v>
       </c>
       <c r="G52" s="0">
-        <v>2.3536511768255863</v>
+        <v>1.3075839871253259</v>
       </c>
       <c r="H52" s="0">
-        <v>2.8063398284383316</v>
+        <v>1.8689996023405084</v>
       </c>
       <c r="I52" s="0">
-        <v>2.917519016504138</v>
+        <v>1.3227145439018082</v>
       </c>
       <c r="J52" s="0">
-        <v>3.2388663967611309</v>
+        <v>1.601030548398968</v>
       </c>
       <c r="K52" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L52" s="0">
-        <v>2.8224426958604147</v>
+        <v>1.6468136721301263</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.712415083193854</v>
+        <v>1.6097272816776593</v>
       </c>
       <c r="B53" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C53" s="0">
-        <v>2.6224020086483448</v>
+        <v>1.5610139616277139</v>
       </c>
       <c r="D53" s="0">
-        <v>2.9476113769143821</v>
+        <v>1.0049767989805967</v>
       </c>
       <c r="E53" s="0">
-        <v>2.6086697097168745</v>
+        <v>1.8192666845669605</v>
       </c>
       <c r="F53" s="0">
-        <v>2.5634028308408809</v>
+        <v>1.4954699268638783</v>
       </c>
       <c r="G53" s="0">
-        <v>2.1323677328505313</v>
+        <v>1.2472339569503106</v>
       </c>
       <c r="H53" s="0">
-        <v>2.6756802817701506</v>
+        <v>1.5451911605976241</v>
       </c>
       <c r="I53" s="0">
-        <v>2.8460209330499868</v>
+        <v>1.1856765506146838</v>
       </c>
       <c r="J53" s="0">
-        <v>2.5763709974236271</v>
+        <v>1.6562384983437601</v>
       </c>
       <c r="K53" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L53" s="0">
-        <v>2.5689671259291491</v>
+        <v>1.6219326345908609</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.6853401594959116</v>
+        <v>1.5949591414787818</v>
       </c>
       <c r="B54" s="0">
-        <v>1.2280701754385954</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C54" s="0">
-        <v>2.5006657451907812</v>
+        <v>1.3606563613538074</v>
       </c>
       <c r="D54" s="0">
-        <v>2.5172504988820212</v>
+        <v>0.8366792489120759</v>
       </c>
       <c r="E54" s="0">
-        <v>2.6050896506459003</v>
+        <v>1.6915779110355307</v>
       </c>
       <c r="F54" s="0">
-        <v>2.4742568133027669</v>
+        <v>1.4317942000509392</v>
       </c>
       <c r="G54" s="0">
-        <v>1.7702675518004409</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H54" s="0">
-        <v>2.2439356927796381</v>
+        <v>1.2952337669715377</v>
       </c>
       <c r="I54" s="0">
-        <v>2.6255685090663521</v>
+        <v>1.1519135667613345</v>
       </c>
       <c r="J54" s="0">
-        <v>2.5211630474788347</v>
+        <v>1.6378358483621627</v>
       </c>
       <c r="K54" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L54" s="0">
-        <v>2.5969582931608222</v>
+        <v>1.3948931670450646</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>2.6459584522989048</v>
+        <v>1.4571231662892574</v>
       </c>
       <c r="B55" s="0">
-        <v>1.8421052631578929</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C55" s="0">
-        <v>2.400486945053828</v>
+        <v>1.2554052169061225</v>
       </c>
       <c r="D55" s="0">
-        <v>1.9931238429543414</v>
+        <v>0.6804029524198778</v>
       </c>
       <c r="E55" s="0">
-        <v>2.4439869924520399</v>
+        <v>1.6599540559085877</v>
       </c>
       <c r="F55" s="0">
-        <v>2.2213732125313808</v>
+        <v>1.4281555870901999</v>
       </c>
       <c r="G55" s="0">
-        <v>1.8306175819754562</v>
+        <v>1.2472339569503106</v>
       </c>
       <c r="H55" s="0">
-        <v>2.050786797704935</v>
+        <v>1.1816167698687712</v>
       </c>
       <c r="I55" s="0">
-        <v>2.5044189787690394</v>
+        <v>1.0009731683581251</v>
       </c>
       <c r="J55" s="0">
-        <v>2.2819285977180694</v>
+        <v>1.601030548398968</v>
       </c>
       <c r="K55" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L55" s="0">
-        <v>2.3294871396137196</v>
+        <v>1.2938139520417991</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>2.6188835286009624</v>
+        <v>1.4743526631879478</v>
       </c>
       <c r="B56" s="0">
-        <v>2.1052631578947349</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C56" s="0">
-        <v>2.2546570461202888</v>
+        <v>1.2224349788863658</v>
       </c>
       <c r="D56" s="0">
-        <v>1.8729113071911123</v>
+        <v>0.71887096386411109</v>
       </c>
       <c r="E56" s="0">
-        <v>2.4141531668605842</v>
+        <v>1.5340553119126452</v>
       </c>
       <c r="F56" s="0">
-        <v>2.1267692755521574</v>
+        <v>1.3972273769239154</v>
       </c>
       <c r="G56" s="0">
-        <v>1.7702675518004409</v>
+        <v>1.5087507543753758</v>
       </c>
       <c r="H56" s="0">
-        <v>1.6758507072658055</v>
+        <v>1.3009146168266761</v>
       </c>
       <c r="I56" s="0">
-        <v>2.303827133522669</v>
+        <v>0.92550296915652042</v>
       </c>
       <c r="J56" s="0">
-        <v>1.8954729481045254</v>
+        <v>1.324990798675008</v>
       </c>
       <c r="K56" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L56" s="0">
-        <v>2.1910863683015562</v>
+        <v>1.3280253786582887</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.4367431328148323</v>
+        <v>1.3094417643004956</v>
       </c>
       <c r="B57" s="0">
-        <v>4.210526315789517</v>
+        <v>0.26315789473684481</v>
       </c>
       <c r="C57" s="0">
-        <v>2.1532101599056763</v>
+        <v>1.0677284774090574</v>
       </c>
       <c r="D57" s="0">
-        <v>1.649315990671524</v>
+        <v>0.77897723174573441</v>
       </c>
       <c r="E57" s="0">
-        <v>2.2948178644947874</v>
+        <v>1.4523106297920732</v>
       </c>
       <c r="F57" s="0">
-        <v>2.1067569042681145</v>
+        <v>1.3626605537969065</v>
       </c>
       <c r="G57" s="0">
-        <v>2.414001207000628</v>
+        <v>1.1667672500503037</v>
       </c>
       <c r="H57" s="0">
-        <v>1.6360847582798554</v>
+        <v>1.1645742203033693</v>
       </c>
       <c r="I57" s="0">
-        <v>2.1548727929932099</v>
+        <v>0.95529383726242756</v>
       </c>
       <c r="J57" s="0">
-        <v>1.4354066985646079</v>
+        <v>0.95693779904307197</v>
       </c>
       <c r="K57" s="0">
-        <v>0</v>
+        <v>0.51546391752577847</v>
       </c>
       <c r="L57" s="0">
-        <v>2.0511305321432114</v>
+        <v>1.2456069418094862</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>2.296445800925468</v>
+        <v>1.1888352860096474</v>
       </c>
       <c r="B58" s="0">
-        <v>4.0350877192982422</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C58" s="0">
-        <v>2.0847335117107728</v>
+        <v>1.0360263254669719</v>
       </c>
       <c r="D58" s="0">
-        <v>1.6925925035462681</v>
+        <v>0.71406246243358196</v>
       </c>
       <c r="E58" s="0">
-        <v>2.2470837435484334</v>
+        <v>1.3144783555595323</v>
       </c>
       <c r="F58" s="0">
-        <v>1.9848633700833225</v>
+        <v>1.1443437761525297</v>
       </c>
       <c r="G58" s="0">
-        <v>1.911084288875476</v>
+        <v>1.3478173405753358</v>
       </c>
       <c r="H58" s="0">
-        <v>1.96557404987786</v>
+        <v>1.2668295176958462</v>
       </c>
       <c r="I58" s="0">
-        <v>2.0079045103374296</v>
+        <v>0.89372604317689741</v>
       </c>
       <c r="J58" s="0">
-        <v>1.821862348178136</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
       </c>
       <c r="L58" s="0">
-        <v>2.0931172829906988</v>
+        <v>1.1818492831151048</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>2.3185980112237847</v>
+        <v>1.2405237767057191</v>
       </c>
       <c r="B59" s="0">
-        <v>3.4210526315789447</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C59" s="0">
-        <v>1.8843759114368666</v>
+        <v>0.96501350511672635</v>
       </c>
       <c r="D59" s="0">
-        <v>1.7454860192820891</v>
+        <v>0.64914769312143816</v>
       </c>
       <c r="E59" s="0">
-        <v>2.1653390614278449</v>
+        <v>1.2285569378561403</v>
       </c>
       <c r="F59" s="0">
-        <v>1.8575119164574447</v>
+        <v>1.1407051631917904</v>
       </c>
       <c r="G59" s="0">
-        <v>2.1122510561255261</v>
+        <v>0.98571715952524564</v>
       </c>
       <c r="H59" s="0">
-        <v>2.1587229449525629</v>
+        <v>1.3065954666818145</v>
       </c>
       <c r="I59" s="0">
-        <v>1.9642112371154479</v>
+        <v>0.84407459633373638</v>
       </c>
       <c r="J59" s="0">
-        <v>1.8034596981965385</v>
+        <v>1.0673536989326453</v>
       </c>
       <c r="K59" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L59" s="0">
-        <v>1.9795975492178006</v>
+        <v>1.1569682455758394</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>2.0970759082406203</v>
+        <v>0.97469725312592215</v>
       </c>
       <c r="B60" s="0">
-        <v>2.6315789473684186</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C60" s="0">
-        <v>1.8298482100964997</v>
+        <v>0.9180943202424573</v>
       </c>
       <c r="D60" s="0">
-        <v>1.7767412785805288</v>
+        <v>0.64914769312143816</v>
       </c>
       <c r="E60" s="0">
-        <v>2.0895611444255482</v>
+        <v>1.1665025806259126</v>
       </c>
       <c r="F60" s="0">
-        <v>1.8374995451733782</v>
+        <v>1.0752101298984818</v>
       </c>
       <c r="G60" s="0">
-        <v>2.1323677328505313</v>
+        <v>0.90525045262522552</v>
       </c>
       <c r="H60" s="0">
-        <v>2.1587229449525629</v>
+        <v>1.2213827188547397</v>
       </c>
       <c r="I60" s="0">
-        <v>1.8152568965859648</v>
+        <v>0.72888323965760293</v>
       </c>
       <c r="J60" s="0">
-        <v>1.5642252484357733</v>
+        <v>0.88332719911667212</v>
       </c>
       <c r="K60" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L60" s="0">
-        <v>1.875408204522127</v>
+        <v>1.0667744844960025</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>2.1635325391355695</v>
+        <v>0.9131633356305987</v>
       </c>
       <c r="B61" s="0">
-        <v>2.0175438596491211</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C61" s="0">
-        <v>1.7753205087561328</v>
+        <v>0.87117513536818803</v>
       </c>
       <c r="D61" s="0">
-        <v>1.6781669992546806</v>
+        <v>0.42795662731709622</v>
       </c>
       <c r="E61" s="0">
-        <v>1.973209224618871</v>
+        <v>1.056714102449356</v>
       </c>
       <c r="F61" s="0">
-        <v>1.6501109776953011</v>
+        <v>0.96605174107630087</v>
       </c>
       <c r="G61" s="0">
-        <v>1.9312009656004812</v>
+        <v>1.2070006035003007</v>
       </c>
       <c r="H61" s="0">
-        <v>1.9087655513264767</v>
+        <v>1.0225529739248984</v>
       </c>
       <c r="I61" s="0">
-        <v>1.6941073662886519</v>
+        <v>0.63355246171873392</v>
       </c>
       <c r="J61" s="0">
-        <v>1.8586676481413307</v>
+        <v>1.159366948840632</v>
       </c>
       <c r="K61" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L61" s="0">
-        <v>1.6405934127453099</v>
+        <v>1.0387833172643291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.9493945062518443</v>
+        <v>0.81963178103770717</v>
       </c>
       <c r="B62" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C62" s="0">
-        <v>1.5774990806375924</v>
+        <v>0.83820489734843129</v>
       </c>
       <c r="D62" s="0">
-        <v>1.6661457456783579</v>
+        <v>0.44238213160868373</v>
       </c>
       <c r="E62" s="0">
-        <v>1.9093648378531562</v>
+        <v>0.98451624451803366</v>
       </c>
       <c r="F62" s="0">
-        <v>1.6155441545682772</v>
+        <v>1.0097150966051733</v>
       </c>
       <c r="G62" s="0">
-        <v>1.2673506336753158</v>
+        <v>0.84490042245021046</v>
       </c>
       <c r="H62" s="0">
-        <v>1.8917230017610618</v>
+        <v>1.0225529739248984</v>
       </c>
       <c r="I62" s="0">
-        <v>1.5550833151278014</v>
+        <v>0.67923179281444201</v>
       </c>
       <c r="J62" s="0">
-        <v>1.821862348178136</v>
+        <v>0.92013249907986661</v>
       </c>
       <c r="K62" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.656144061207351</v>
+        <v>0.93459397256865517</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.8140198877621327</v>
+        <v>0.78763414394013909</v>
       </c>
       <c r="B63" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C63" s="0">
-        <v>1.5153628628311275</v>
+        <v>0.79635805678489391</v>
       </c>
       <c r="D63" s="0">
-        <v>1.3704229077008139</v>
+        <v>0.35823335657442323</v>
       </c>
       <c r="E63" s="0">
-        <v>1.8485038336465869</v>
+        <v>0.85981085354574938</v>
       </c>
       <c r="F63" s="0">
-        <v>1.566422879598296</v>
+        <v>0.91329185314558003</v>
       </c>
       <c r="G63" s="0">
-        <v>1.3478173405753358</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H63" s="0">
-        <v>1.664489007555529</v>
+        <v>0.92597852638754685</v>
       </c>
       <c r="I63" s="0">
-        <v>1.5054318682846406</v>
+        <v>0.57595678338066725</v>
       </c>
       <c r="J63" s="0">
-        <v>1.4906146485093841</v>
+        <v>1.0121457489878534</v>
       </c>
       <c r="K63" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.6001617267440038</v>
+        <v>0.89260722172114493</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.7672541104656871</v>
+        <v>0.76794329034163567</v>
       </c>
       <c r="B64" s="0">
-        <v>0.96491228070175361</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C64" s="0">
-        <v>1.4418138703255163</v>
+        <v>0.71012820350245309</v>
       </c>
       <c r="D64" s="0">
-        <v>1.0722958190080052</v>
+        <v>0.28370158440122112</v>
       </c>
       <c r="E64" s="0">
-        <v>1.7393120319818596</v>
+        <v>0.79536979026820531</v>
       </c>
       <c r="F64" s="0">
-        <v>1.5573263471964474</v>
+        <v>0.89146017538114386</v>
       </c>
       <c r="G64" s="0">
-        <v>1.2271172802253056</v>
+        <v>0.62361697847515529</v>
       </c>
       <c r="H64" s="0">
-        <v>1.4429358632051343</v>
+        <v>0.89757427711185522</v>
       </c>
       <c r="I64" s="0">
-        <v>1.4299616690830359</v>
+        <v>0.54616591527477065</v>
       </c>
       <c r="J64" s="0">
-        <v>1.6930437983069548</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K64" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.5177432898951873</v>
+        <v>0.88794202718253279</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.4718913064881349</v>
+        <v>0.65718223885005356</v>
       </c>
       <c r="B65" s="0">
-        <v>0.52631578947368374</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C65" s="0">
-        <v>1.422792579160272</v>
+        <v>0.6492600717736714</v>
       </c>
       <c r="D65" s="0">
-        <v>1.0025725482653323</v>
+        <v>0.24282932224172316</v>
       </c>
       <c r="E65" s="0">
-        <v>1.6211700826396953</v>
+        <v>0.72913869745517401</v>
       </c>
       <c r="F65" s="0">
-        <v>1.4190590546883515</v>
+        <v>0.83324236800931417</v>
       </c>
       <c r="G65" s="0">
-        <v>1.1868839267752955</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H65" s="0">
-        <v>1.3009146168266761</v>
+        <v>0.92029767653240835</v>
       </c>
       <c r="I65" s="0">
-        <v>1.2114953029731275</v>
+        <v>0.51240293142142113</v>
       </c>
       <c r="J65" s="0">
-        <v>1.6562384983437601</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K65" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>1.3933381021988605</v>
+        <v>0.76042670979379767</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.5826523579797172</v>
+        <v>0.63256867185192422</v>
       </c>
       <c r="B66" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.4035087719298234</v>
       </c>
       <c r="C66" s="0">
-        <v>1.2769626802267326</v>
+        <v>0.63404303884147606</v>
       </c>
       <c r="D66" s="0">
-        <v>0.83187074748154655</v>
+        <v>0.29091433654701487</v>
       </c>
       <c r="E66" s="0">
-        <v>1.5453921656373983</v>
+        <v>0.6408305737044655</v>
       </c>
       <c r="F66" s="0">
-        <v>1.4226976676490908</v>
+        <v>0.69315576902084863</v>
       </c>
       <c r="G66" s="0">
-        <v>1.4282840474753558</v>
+        <v>0.62361697847515529</v>
       </c>
       <c r="H66" s="0">
-        <v>1.3634039652331977</v>
+        <v>0.65897858319604552</v>
       </c>
       <c r="I66" s="0">
-        <v>1.2214255923417598</v>
+        <v>0.47466783182061878</v>
       </c>
       <c r="J66" s="0">
-        <v>1.3801987486198</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K66" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>1.3482412216589419</v>
+        <v>0.81951917394955298</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.503888943585703</v>
+        <v>0.62764595845229831</v>
       </c>
       <c r="B67" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C67" s="0">
-        <v>1.1920009130219749</v>
+        <v>0.55288552986976713</v>
       </c>
       <c r="D67" s="0">
-        <v>0.72848796672516947</v>
+        <v>0.29572283797754406</v>
       </c>
       <c r="E67" s="0">
-        <v>1.4135266565231646</v>
+        <v>0.58474298159252913</v>
       </c>
       <c r="F67" s="0">
-        <v>1.3262744241894979</v>
+        <v>0.72408397918713319</v>
       </c>
       <c r="G67" s="0">
-        <v>1.4886340776503708</v>
+        <v>0.60350030175015035</v>
       </c>
       <c r="H67" s="0">
-        <v>1.192978469579048</v>
+        <v>0.72146793160256717</v>
       </c>
       <c r="I67" s="0">
-        <v>1.0645270203173711</v>
+        <v>0.41707215348255211</v>
       </c>
       <c r="J67" s="0">
-        <v>0.97534044902465866</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K67" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>1.3015892762728194</v>
+        <v>0.78530774733306319</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.4595845229890703</v>
+        <v>0.54395983065865861</v>
       </c>
       <c r="B68" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C68" s="0">
-        <v>1.1222561787494125</v>
+        <v>0.50596634499549786</v>
       </c>
       <c r="D68" s="0">
-        <v>0.8006154881831069</v>
+        <v>0.26687182939436899</v>
       </c>
       <c r="E68" s="0">
-        <v>1.4248635102479179</v>
+        <v>0.52626868343327626</v>
       </c>
       <c r="F68" s="0">
-        <v>1.2516828584943407</v>
+        <v>0.68405923661900025</v>
       </c>
       <c r="G68" s="0">
-        <v>1.1667672500502908</v>
+        <v>0.64373365520016035</v>
       </c>
       <c r="H68" s="0">
-        <v>1.3463614156677828</v>
+        <v>0.59080838493438559</v>
       </c>
       <c r="I68" s="0">
-        <v>1.0267919207165688</v>
+        <v>0.3991976326190142</v>
       </c>
       <c r="J68" s="0">
-        <v>0.99374309900625601</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K68" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>1.2487170715018805</v>
+        <v>0.65623736509812403</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.3758983951954458</v>
+        <v>0.53165304715959982</v>
       </c>
       <c r="B69" s="0">
-        <v>0.17543859649122986</v>
+        <v>0.43859649122807465</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0575837887875938</v>
+        <v>0.43368543856757441</v>
       </c>
       <c r="D69" s="0">
-        <v>0.69963695814200211</v>
+        <v>0.27648883225543042</v>
       </c>
       <c r="E69" s="0">
-        <v>1.2202034666905461</v>
+        <v>0.50001491691280087</v>
       </c>
       <c r="F69" s="0">
-        <v>1.1370665502310635</v>
+        <v>0.59127460612015304</v>
       </c>
       <c r="G69" s="0">
-        <v>1.367934017300356</v>
+        <v>0.44256688795011517</v>
       </c>
       <c r="H69" s="0">
-        <v>1.3236380162472441</v>
+        <v>0.80668067942965094</v>
       </c>
       <c r="I69" s="0">
-        <v>0.98707076324205101</v>
+        <v>0.34756012790213059</v>
       </c>
       <c r="J69" s="0">
-        <v>1.1593669488406448</v>
+        <v>0.69930069930070649</v>
       </c>
       <c r="K69" s="0">
-        <v>0.25773195876288924</v>
+        <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>1.0745498087270349</v>
+        <v>0.67334307840637642</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.2306783499064673</v>
+        <v>0.50457812346165165</v>
       </c>
       <c r="B70" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0423667558553864</v>
+        <v>0.33477472450829932</v>
       </c>
       <c r="D70" s="0">
-        <v>0.72848796672516947</v>
+        <v>0.21157406294328352</v>
       </c>
       <c r="E70" s="0">
-        <v>1.2040932008711467</v>
+        <v>0.4093200871147703</v>
       </c>
       <c r="F70" s="0">
-        <v>1.0934031947021785</v>
+        <v>0.54397263763053472</v>
       </c>
       <c r="G70" s="0">
-        <v>1.0661838664252656</v>
+        <v>0.5833836250251454</v>
       </c>
       <c r="H70" s="0">
-        <v>1.1361699710276647</v>
+        <v>0.62489348406521561</v>
       </c>
       <c r="I70" s="0">
-        <v>0.92550296915652042</v>
+        <v>0.36543464876566473</v>
       </c>
       <c r="J70" s="0">
-        <v>1.1777695988222294</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K70" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>1.1569682455758394</v>
+        <v>0.55204802040245027</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.2897509107019778</v>
+        <v>0.45781234616520589</v>
       </c>
       <c r="B71" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C71" s="0">
-        <v>0.99037522667038547</v>
+        <v>0.3246300358868357</v>
       </c>
       <c r="D71" s="0">
-        <v>0.59144567595508812</v>
+        <v>0.24763782367225232</v>
       </c>
       <c r="E71" s="0">
-        <v>1.1139950475849509</v>
+        <v>0.38306632059428947</v>
       </c>
       <c r="F71" s="0">
-        <v>1.0934031947021785</v>
+        <v>0.52032165338572889</v>
       </c>
       <c r="G71" s="0">
-        <v>1.1265338966002805</v>
+        <v>0.48280024140012029</v>
       </c>
       <c r="H71" s="0">
-        <v>1.1077657217519732</v>
+        <v>0.61353178435493894</v>
       </c>
       <c r="I71" s="0">
-        <v>0.85003276995491583</v>
+        <v>0.29790868105896579</v>
       </c>
       <c r="J71" s="0">
-        <v>0.88332719911667212</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K71" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>1.0185674742636759</v>
+        <v>0.54582776101763397</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.1396081520133887</v>
+        <v>0.41104656886876012</v>
       </c>
       <c r="B72" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C72" s="0">
-        <v>0.94852838610684809</v>
+        <v>0.2967321421778108</v>
       </c>
       <c r="D72" s="0">
-        <v>0.52412665592767971</v>
+        <v>0.15868054720746266</v>
       </c>
       <c r="E72" s="0">
-        <v>1.0406038366299701</v>
+        <v>0.31743190429308721</v>
       </c>
       <c r="F72" s="0">
-        <v>0.95513590219408284</v>
+        <v>0.43845286176909321</v>
       </c>
       <c r="G72" s="0">
-        <v>0.92536712935023058</v>
+        <v>0.34198350432508523</v>
       </c>
       <c r="H72" s="0">
-        <v>1.0566380730557283</v>
+        <v>0.46582968812134257</v>
       </c>
       <c r="I72" s="0">
-        <v>0.83811642271255715</v>
+        <v>0.27010387082679566</v>
       </c>
       <c r="J72" s="0">
-        <v>0.93853514906146396</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K72" s="0">
         <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.94392436164587978</v>
+        <v>0.49140049140049097</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.0091562469233033</v>
+        <v>0.35443536477306259</v>
       </c>
       <c r="B73" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C73" s="0">
-        <v>0.87624747967891992</v>
+        <v>0.23205975221598021</v>
       </c>
       <c r="D73" s="0">
-        <v>0.47844589233765256</v>
+        <v>0.1178082850479647</v>
       </c>
       <c r="E73" s="0">
-        <v>0.86697097168769865</v>
+        <v>0.28342134311882788</v>
       </c>
       <c r="F73" s="0">
-        <v>0.98242549939962809</v>
+        <v>0.46938107193537776</v>
       </c>
       <c r="G73" s="0">
-        <v>0.68396700865017046</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H73" s="0">
-        <v>0.95438277566323837</v>
+        <v>0.35221269101857611</v>
       </c>
       <c r="I73" s="0">
-        <v>0.68518996643562136</v>
+        <v>0.22442453973108756</v>
       </c>
       <c r="J73" s="0">
-        <v>1.0121457489878534</v>
+        <v>0.47846889952153066</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.96414020464653283</v>
+        <v>0.44008335147575617</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.95992911292704441</v>
+        <v>0.31505365757605563</v>
       </c>
       <c r="B74" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C74" s="0">
-        <v>0.77099633523123479</v>
+        <v>0.19401716988549164</v>
       </c>
       <c r="D74" s="0">
-        <v>0.37025461015074618</v>
+        <v>0.10578703147164176</v>
       </c>
       <c r="E74" s="0">
-        <v>0.82639696888331915</v>
+        <v>0.23628389868432806</v>
       </c>
       <c r="F74" s="0">
-        <v>0.92238838554742841</v>
+        <v>0.48211621729796561</v>
       </c>
       <c r="G74" s="0">
-        <v>0.62361697847515529</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H74" s="0">
-        <v>0.94870192580810009</v>
+        <v>0.40334033971482097</v>
       </c>
       <c r="I74" s="0">
-        <v>0.60773370936029025</v>
+        <v>0.22839665547854046</v>
       </c>
       <c r="J74" s="0">
-        <v>1.0305483989694506</v>
+        <v>0.47846889952153066</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.82729449818057343</v>
+        <v>0.45563399993779702</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.78517278724032613</v>
+        <v>0.28305602047848749</v>
       </c>
       <c r="B75" s="0">
-        <v>1.0526315789473675</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.76211973268745414</v>
+        <v>0.12300434953524633</v>
       </c>
       <c r="D75" s="0">
-        <v>0.35102060442862953</v>
+        <v>0.069723270742672983</v>
       </c>
       <c r="E75" s="0">
-        <v>0.75897252304662954</v>
+        <v>0.21540022077030918</v>
       </c>
       <c r="F75" s="0">
-        <v>0.86780919113633803</v>
+        <v>0.38751228031874213</v>
       </c>
       <c r="G75" s="0">
-        <v>0.48280024140012029</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H75" s="0">
-        <v>0.85780832812588681</v>
+        <v>0.30676589217746947</v>
       </c>
       <c r="I75" s="0">
-        <v>0.64149669321363967</v>
+        <v>0.15689857202438864</v>
       </c>
       <c r="J75" s="0">
-        <v>0.86492454913507477</v>
+        <v>0.58888479941111471</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.81485397941094084</v>
+        <v>0.38099088732000091</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.78271143054051329</v>
+        <v>0.24121295658166758</v>
       </c>
       <c r="B76" s="0">
-        <v>0.78947368421052566</v>
+        <v>0</v>
       </c>
       <c r="C76" s="0">
-        <v>0.67462179332733052</v>
+        <v>0.11920009130219748</v>
       </c>
       <c r="D76" s="0">
-        <v>0.27648883225542736</v>
+        <v>0.093765777895318841</v>
       </c>
       <c r="E76" s="0">
-        <v>0.6408305737044655</v>
+        <v>0.21957695635311297</v>
       </c>
       <c r="F76" s="0">
-        <v>0.78412109303933275</v>
+        <v>0.3347523923880214</v>
       </c>
       <c r="G76" s="0">
-        <v>0.78455039227519552</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H76" s="0">
-        <v>0.79531897971936527</v>
+        <v>0.35789354087371439</v>
       </c>
       <c r="I76" s="0">
-        <v>0.58985918849675223</v>
+        <v>0.14895434052948289</v>
       </c>
       <c r="J76" s="0">
-        <v>0.90172984909826925</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>0.80241346064130803</v>
+        <v>0.38410101701240906</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.77778871714088738</v>
+        <v>0.2215221029831641</v>
       </c>
       <c r="B77" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C77" s="0">
-        <v>0.62643452237537822</v>
+        <v>0.10778731660305091</v>
       </c>
       <c r="D77" s="0">
-        <v>0.31976534513018989</v>
+        <v>0.069723270742672983</v>
       </c>
       <c r="E77" s="0">
-        <v>0.61517348369581382</v>
+        <v>0.15155583400459427</v>
       </c>
       <c r="F77" s="0">
-        <v>0.72226467270676353</v>
+        <v>0.27653458501619155</v>
       </c>
       <c r="G77" s="0">
-        <v>0.78455039227519552</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H77" s="0">
-        <v>0.68738283247173715</v>
+        <v>0.24995739362608624</v>
       </c>
       <c r="I77" s="0">
-        <v>0.57794284125439366</v>
+        <v>0.1390240511608507</v>
       </c>
       <c r="J77" s="0">
-        <v>0.5152741994847253</v>
+        <v>0.36805299963194671</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L77" s="0">
-        <v>0.79463813641028769</v>
+        <v>0.31412309893322521</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.681795805848183</v>
+        <v>0.18706310918578303</v>
       </c>
       <c r="B78" s="0">
-        <v>1.5789473684210513</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>0.57444299319037728</v>
+        <v>0.060868131728781694</v>
       </c>
       <c r="D78" s="0">
-        <v>0.25004207438751691</v>
+        <v>0.093765777895318841</v>
       </c>
       <c r="E78" s="0">
-        <v>0.51314180017303579</v>
+        <v>0.13246218562606271</v>
       </c>
       <c r="F78" s="0">
-        <v>0.64767310701160663</v>
+        <v>0.25288360077138572</v>
       </c>
       <c r="G78" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H78" s="0">
-        <v>0.74419133102312041</v>
+        <v>0.20451059478497965</v>
       </c>
       <c r="I78" s="0">
-        <v>0.48062600544179812</v>
+        <v>0.12114953029731276</v>
       </c>
       <c r="J78" s="0">
-        <v>0.68089804931910136</v>
+        <v>0.22083179977916803</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.71532982925387922</v>
+        <v>0.25814076446987816</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.67933444914837005</v>
+        <v>0.15506547208821489</v>
       </c>
       <c r="B79" s="0">
-        <v>1.2280701754385954</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C79" s="0">
-        <v>0.53766849693757157</v>
+        <v>0.041846840563537414</v>
       </c>
       <c r="D79" s="0">
-        <v>0.27408458154016274</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E79" s="0">
-        <v>0.46839106178585238</v>
+        <v>0.10978847817655649</v>
       </c>
       <c r="F79" s="0">
-        <v>0.64585380053123698</v>
+        <v>0.19466579339955592</v>
       </c>
       <c r="G79" s="0">
-        <v>0.46268356467511529</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H79" s="0">
-        <v>0.62489348406521561</v>
+        <v>0.15338294608873473</v>
       </c>
       <c r="I79" s="0">
-        <v>0.50843081567396831</v>
+        <v>0.11121924092868056</v>
       </c>
       <c r="J79" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.64379684632849132</v>
+        <v>0.21926414331477603</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.59072560795510431</v>
+        <v>0.11322240819139499</v>
       </c>
       <c r="B80" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C80" s="0">
-        <v>0.47426419305342404</v>
+        <v>0.038042582330488559</v>
       </c>
       <c r="D80" s="0">
-        <v>0.30533984083860238</v>
+        <v>0.062510518596879228</v>
       </c>
       <c r="E80" s="0">
-        <v>0.44810406038366263</v>
+        <v>0.092484859333512248</v>
       </c>
       <c r="F80" s="0">
-        <v>0.60037113852199486</v>
+        <v>0.1673761961940107</v>
       </c>
       <c r="G80" s="0">
-        <v>0.42245021122510523</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H80" s="0">
-        <v>0.61921263421007733</v>
+        <v>0.18178719536442634</v>
       </c>
       <c r="I80" s="0">
-        <v>0.45679331095708092</v>
+        <v>0.053623562590613842</v>
       </c>
       <c r="J80" s="0">
-        <v>0.60728744939271206</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K80" s="0">
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.57381892824930747</v>
+        <v>0.18038752215967391</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.52426897706015507</v>
+        <v>0.059072560795510431</v>
       </c>
       <c r="B81" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C81" s="0">
-        <v>0.40705563093622754</v>
+        <v>0.022825549398293135</v>
       </c>
       <c r="D81" s="0">
-        <v>0.26446757867910442</v>
+        <v>0.033659510013704201</v>
       </c>
       <c r="E81" s="0">
-        <v>0.41469017572123235</v>
+        <v>0.073987887466809801</v>
       </c>
       <c r="F81" s="0">
-        <v>0.60219044500236452</v>
+        <v>0.14372521194920485</v>
       </c>
       <c r="G81" s="0">
-        <v>0.46268356467511529</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H81" s="0">
-        <v>0.59648923478952398</v>
+        <v>0.19882974492984132</v>
       </c>
       <c r="I81" s="0">
-        <v>0.37735099600802335</v>
+        <v>0.043693273221981653</v>
       </c>
       <c r="J81" s="0">
-        <v>0.62569009937430942</v>
+        <v>0.11041589988958402</v>
       </c>
       <c r="K81" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L81" s="0">
-        <v>0.56759866886449117</v>
+        <v>0.15861661431281671</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.49719405336221834</v>
+        <v>0.095992911292705527</v>
       </c>
       <c r="B82" s="0">
-        <v>0.43859649122807465</v>
+        <v>0.26315789473684481</v>
       </c>
       <c r="C82" s="0">
-        <v>0.36267261821732832</v>
+        <v>0.017753205087561525</v>
       </c>
       <c r="D82" s="0">
-        <v>0.23321231938066739</v>
+        <v>0.036063760728969184</v>
       </c>
       <c r="E82" s="0">
-        <v>0.35382917151466692</v>
+        <v>0.045944091410842082</v>
       </c>
       <c r="F82" s="0">
-        <v>0.43117563584761931</v>
+        <v>0.098242549939963897</v>
       </c>
       <c r="G82" s="0">
-        <v>0.32186682760008378</v>
+        <v>0.14081673707503664</v>
       </c>
       <c r="H82" s="0">
-        <v>0.6248934840652226</v>
+        <v>0.11929784695790611</v>
       </c>
       <c r="I82" s="0">
-        <v>0.33564378065977185</v>
+        <v>0.043693273221982139</v>
       </c>
       <c r="J82" s="0">
-        <v>0.53367684946632865</v>
+        <v>0.12881854987118277</v>
       </c>
       <c r="K82" s="0">
         <v>0.12886597938144462</v>
       </c>
       <c r="L82" s="0">
-        <v>0.5287220477093949</v>
+        <v>0.12751531738873642</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.47750319976370936</v>
+        <v>0.059072560795510431</v>
       </c>
       <c r="B83" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C83" s="0">
-        <v>0.29419597002244485</v>
+        <v>0.01268086077682952</v>
       </c>
       <c r="D83" s="0">
-        <v>0.20436131079748976</v>
+        <v>0.021638256437381268</v>
       </c>
       <c r="E83" s="0">
-        <v>0.28998478474894812</v>
+        <v>0.038783973268892234</v>
       </c>
       <c r="F83" s="0">
-        <v>0.44573008769057193</v>
+        <v>0.076410872175526626</v>
       </c>
       <c r="G83" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H83" s="0">
-        <v>0.46582968812134257</v>
+        <v>0.05680849855138323</v>
       </c>
       <c r="I83" s="0">
-        <v>0.3237274334174095</v>
+        <v>0.033762983853349457</v>
       </c>
       <c r="J83" s="0">
-        <v>0.44166359955833606</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K83" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L83" s="0">
-        <v>0.51939165863216452</v>
+        <v>0.08552856654122469</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.49719405336221284</v>
+        <v>0.039381707197006954</v>
       </c>
       <c r="B84" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C84" s="0">
-        <v>0.22064697751683363</v>
+        <v>0.011412774699146568</v>
       </c>
       <c r="D84" s="0">
-        <v>0.13223378933955221</v>
+        <v>0.012021253576322928</v>
       </c>
       <c r="E84" s="0">
-        <v>0.2750678719532203</v>
+        <v>0.031027178615113789</v>
       </c>
       <c r="F84" s="0">
-        <v>0.44209147472983257</v>
+        <v>0.040024742568132987</v>
       </c>
       <c r="G84" s="0">
-        <v>0.36210018105009018</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H84" s="0">
-        <v>0.40334033971482097</v>
+        <v>0.051127648696244914</v>
       </c>
       <c r="I84" s="0">
-        <v>0.28599233381660716</v>
+        <v>0.029790868105896578</v>
       </c>
       <c r="J84" s="0">
-        <v>0.31284504968715471</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K84" s="0">
-        <v>0</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L84" s="0">
-        <v>0.42608776785991936</v>
+        <v>0.08552856654122469</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.36920350497194021</v>
+        <v>0.034458993797381085</v>
       </c>
       <c r="B85" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C85" s="0">
-        <v>0.21050228889537004</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D85" s="0">
-        <v>0.098574279325848016</v>
+        <v>0.014425504291587513</v>
       </c>
       <c r="E85" s="0">
-        <v>0.21420686774665099</v>
+        <v>0.016706942331215117</v>
       </c>
       <c r="F85" s="0">
-        <v>0.38933158679911184</v>
+        <v>0.045482662009242031</v>
       </c>
       <c r="G85" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H85" s="0">
-        <v>0.38061694029426768</v>
+        <v>0.05680849855138323</v>
       </c>
       <c r="I85" s="0">
-        <v>0.26414569720561631</v>
+        <v>0.017874520863537947</v>
       </c>
       <c r="J85" s="0">
-        <v>0.5152741994847253</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K85" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L85" s="0">
-        <v>0.38099088732000091</v>
+        <v>0.038876621155102133</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.36920350497194021</v>
+        <v>0.019690853598503477</v>
       </c>
       <c r="B86" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C86" s="0">
-        <v>0.16485119009878377</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D86" s="0">
-        <v>0.088957276464789667</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E86" s="0">
-        <v>0.18914645424982829</v>
+        <v>0.010740177212924003</v>
       </c>
       <c r="F86" s="0">
-        <v>0.40388603864206929</v>
+        <v>0.038205436087763313</v>
       </c>
       <c r="G86" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H86" s="0">
-        <v>0.2556382434812246</v>
+        <v>0.045446798841106584</v>
       </c>
       <c r="I86" s="0">
-        <v>0.23832694484717262</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J86" s="0">
-        <v>0.4600662495399333</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K86" s="0">
-        <v>0</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L86" s="0">
-        <v>0.35610984978073557</v>
+        <v>0.02954623207787762</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.2559810967805452</v>
+        <v>0.014768140198877608</v>
       </c>
       <c r="B87" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C87" s="0">
-        <v>0.11920009130219748</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D87" s="0">
-        <v>0.084148775034260492</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E87" s="0">
-        <v>0.17959963006056251</v>
+        <v>0.0095468241892657808</v>
       </c>
       <c r="F87" s="0">
-        <v>0.33293308590765169</v>
+        <v>0.010915838882218089</v>
       </c>
       <c r="G87" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H87" s="0">
-        <v>0.35221269101857611</v>
+        <v>0.028404249275691615</v>
       </c>
       <c r="I87" s="0">
-        <v>0.20655001886754962</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J87" s="0">
-        <v>0.27603974972396</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K87" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L87" s="0">
-        <v>0.30479270985600077</v>
+        <v>0.024881037539265367</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.27321059367923578</v>
+        <v>0.0049227133996258693</v>
       </c>
       <c r="B88" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C88" s="0">
-        <v>0.082425595049391884</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D88" s="0">
-        <v>0.091361527180054247</v>
+        <v>0</v>
       </c>
       <c r="E88" s="0">
-        <v>0.13902562725618295</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F88" s="0">
-        <v>0.2619801331732341</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G88" s="0">
-        <v>0.20116676725005009</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H88" s="0">
-        <v>0.27268079304663956</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I88" s="0">
-        <v>0.20456396099382318</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J88" s="0">
-        <v>0.27603974972396</v>
+        <v>0</v>
       </c>
       <c r="K88" s="0">
-        <v>0</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L88" s="0">
-        <v>0.27835660747053126</v>
+        <v>0.015550648462040852</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.22398345968297706</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B89" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C89" s="0">
-        <v>0.055795787418049886</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D89" s="0">
-        <v>0.076936022888466751</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E89" s="0">
-        <v>0.13007547957874627</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F89" s="0">
-        <v>0.24924498781064636</v>
+        <v>0.010915838882218089</v>
       </c>
       <c r="G89" s="0">
-        <v>0.18105009052504509</v>
+        <v>0</v>
       </c>
       <c r="H89" s="0">
-        <v>0.24995739362608624</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I89" s="0">
-        <v>0.15888462989811508</v>
+        <v>0</v>
       </c>
       <c r="J89" s="0">
-        <v>0.23923444976076533</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K89" s="0">
-        <v>0</v>
+        <v>1.417525773195875</v>
       </c>
       <c r="L89" s="0">
-        <v>0.21926414331477603</v>
+        <v>0.013995583615836769</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.22398345968297706</v>
+        <v>0</v>
       </c>
       <c r="B90" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C90" s="0">
-        <v>0.049455357029635126</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.086553025749525073</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0">
-        <v>0.084131388167904692</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F90" s="0">
-        <v>0.19648509987992563</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G90" s="0">
-        <v>0.22128344397505512</v>
+        <v>0</v>
       </c>
       <c r="H90" s="0">
-        <v>0.11361699710276646</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I90" s="0">
-        <v>0.13107981966594495</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J90" s="0">
-        <v>0.165623849834376</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K90" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L90" s="0">
-        <v>0.23170466208440874</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.19936989268484773</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B91" s="0">
         <v>0</v>
       </c>
       <c r="C91" s="0">
-        <v>0.04565109879658627</v>
+        <v>0</v>
       </c>
       <c r="D91" s="0">
-        <v>0.064914769312143808</v>
+        <v>0</v>
       </c>
       <c r="E91" s="0">
-        <v>0.072794534443151579</v>
+        <v>0</v>
       </c>
       <c r="F91" s="0">
-        <v>0.14372521194920485</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G91" s="0">
-        <v>0.080466706900020044</v>
+        <v>0</v>
       </c>
       <c r="H91" s="0">
-        <v>0.22155314435039461</v>
+        <v>0</v>
       </c>
       <c r="I91" s="0">
-        <v>0.11916347242358631</v>
+        <v>0</v>
       </c>
       <c r="J91" s="0">
-        <v>0.23923444976076533</v>
+        <v>0</v>
       </c>
       <c r="K91" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L91" s="0">
-        <v>0.16639193854383713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.13537461848971141</v>
+        <v>0.0049227133996258693</v>
       </c>
       <c r="B92" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0.040578754485854462</v>
+        <v>0</v>
       </c>
       <c r="D92" s="0">
-        <v>0.06010626788161464</v>
+        <v>0</v>
       </c>
       <c r="E92" s="0">
-        <v>0.056087592111936459</v>
+        <v>0</v>
       </c>
       <c r="F92" s="0">
-        <v>0.13462867954735641</v>
+        <v>0</v>
       </c>
       <c r="G92" s="0">
-        <v>0.10058338362502504</v>
+        <v>0</v>
       </c>
       <c r="H92" s="0">
-        <v>0.13065954666818144</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I92" s="0">
-        <v>0.089372604317689744</v>
+        <v>0</v>
       </c>
       <c r="J92" s="0">
-        <v>0.20242914979757068</v>
+        <v>0</v>
       </c>
       <c r="K92" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L92" s="0">
-        <v>0.1570615494666126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.11814512159102086</v>
+        <v>0</v>
       </c>
       <c r="B93" s="0">
-        <v>0.35087719298245584</v>
+        <v>0</v>
       </c>
       <c r="C93" s="0">
-        <v>0.024093635475976087</v>
+        <v>0</v>
       </c>
       <c r="D93" s="0">
-        <v>0.055297766451085466</v>
+        <v>0</v>
       </c>
       <c r="E93" s="0">
-        <v>0.044154061875354242</v>
+        <v>0</v>
       </c>
       <c r="F93" s="0">
-        <v>0.096423243459593119</v>
+        <v>0</v>
       </c>
       <c r="G93" s="0">
-        <v>0.14081673707503506</v>
+        <v>0</v>
       </c>
       <c r="H93" s="0">
-        <v>0.14202124637845809</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I93" s="0">
-        <v>0.089372604317689744</v>
+        <v>0</v>
       </c>
       <c r="J93" s="0">
-        <v>0.12881854987118133</v>
+        <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L93" s="0">
-        <v>0.090193761079836954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.088608841193266633</v>
+        <v>0</v>
       </c>
       <c r="B94" s="0">
-        <v>0.17543859649122986</v>
+        <v>0</v>
       </c>
       <c r="C94" s="0">
-        <v>0.0088766025437807625</v>
+        <v>0</v>
       </c>
       <c r="D94" s="0">
-        <v>0.040872262159498414</v>
+        <v>0</v>
       </c>
       <c r="E94" s="0">
-        <v>0.035203914197917956</v>
+        <v>0</v>
       </c>
       <c r="F94" s="0">
-        <v>0.05094058145035165</v>
+        <v>0</v>
       </c>
       <c r="G94" s="0">
-        <v>0.020116676725005236</v>
+        <v>0</v>
       </c>
       <c r="H94" s="0">
-        <v>0.090893597682214181</v>
+        <v>0</v>
       </c>
       <c r="I94" s="0">
-        <v>0.049651446843161515</v>
+        <v>0</v>
       </c>
       <c r="J94" s="0">
-        <v>0.11041589988958524</v>
+        <v>0</v>
       </c>
       <c r="K94" s="0">
-        <v>0.64432989690722309</v>
+        <v>0</v>
       </c>
       <c r="L94" s="0">
-        <v>0.080863372002613343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.071379344294575112</v>
+        <v>0</v>
       </c>
       <c r="B95" s="0">
         <v>0</v>
       </c>
       <c r="C95" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0</v>
       </c>
       <c r="D95" s="0">
-        <v>0.019234005722116688</v>
+        <v>0</v>
       </c>
       <c r="E95" s="0">
-        <v>0.017900295354873339</v>
+        <v>0</v>
       </c>
       <c r="F95" s="0">
-        <v>0.032747516646654262</v>
+        <v>0</v>
       </c>
       <c r="G95" s="0">
         <v>0</v>
       </c>
       <c r="H95" s="0">
-        <v>0.051127648696244914</v>
+        <v>0</v>
       </c>
       <c r="I95" s="0">
-        <v>0.041707215348255215</v>
+        <v>0</v>
       </c>
       <c r="J95" s="0">
-        <v>0.073610599926389339</v>
+        <v>0</v>
       </c>
       <c r="K95" s="0">
-        <v>1.1597938144329887</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L95" s="0">
-        <v>0.065312723540571577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.041843063896819889</v>
+        <v>0</v>
       </c>
       <c r="B96" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C96" s="0">
-        <v>0.011412774699146568</v>
+        <v>0</v>
       </c>
       <c r="D96" s="0">
-        <v>0.012021253576322928</v>
+        <v>0</v>
       </c>
       <c r="E96" s="0">
-        <v>0.013723559772069561</v>
+        <v>0</v>
       </c>
       <c r="F96" s="0">
-        <v>0.040024742568132987</v>
+        <v>0</v>
       </c>
       <c r="G96" s="0">
         <v>0</v>
       </c>
       <c r="H96" s="0">
-        <v>0.028404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I96" s="0">
-        <v>0.031776925979623019</v>
+        <v>0</v>
       </c>
       <c r="J96" s="0">
-        <v>0.055207949944792008</v>
+        <v>0</v>
       </c>
       <c r="K96" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0.031101296924081704</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.049227133996258693</v>
+        <v>0</v>
       </c>
       <c r="B97" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C97" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0</v>
       </c>
       <c r="D97" s="0">
         <v>0</v>
       </c>
       <c r="E97" s="0">
-        <v>0.0041767355828037792</v>
+        <v>0</v>
       </c>
       <c r="F97" s="0">
-        <v>0.016373758323327131</v>
+        <v>0</v>
       </c>
       <c r="G97" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H97" s="0">
-        <v>0.034085099130829945</v>
+        <v>0</v>
       </c>
       <c r="I97" s="0">
-        <v>0.02780481023217014</v>
+        <v>0</v>
       </c>
       <c r="J97" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K97" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L97" s="0">
-        <v>0.027991167231673539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.03199763709756815</v>
+        <v>0</v>
       </c>
       <c r="B98" s="0">
-        <v>0.35087719298245584</v>
+        <v>0</v>
       </c>
       <c r="C98" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D98" s="0">
         <v>0</v>
       </c>
       <c r="E98" s="0">
-        <v>0.0041767355828037792</v>
+        <v>0</v>
       </c>
       <c r="F98" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0</v>
       </c>
       <c r="G98" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H98" s="0">
-        <v>0.022723399420553292</v>
+        <v>0</v>
       </c>
       <c r="I98" s="0">
-        <v>0.011916347242358632</v>
+        <v>0</v>
       </c>
       <c r="J98" s="0">
-        <v>0.055207949944792008</v>
+        <v>0</v>
       </c>
       <c r="K98" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L98" s="0">
-        <v>0.02021584300065311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0</v>
       </c>
       <c r="B99" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C99" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D99" s="0">
         <v>0</v>
       </c>
       <c r="E99" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0</v>
       </c>
       <c r="F99" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0</v>
       </c>
       <c r="G99" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H99" s="0">
-        <v>0.022723399420553292</v>
+        <v>0</v>
       </c>
       <c r="I99" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0</v>
       </c>
       <c r="J99" s="0">
         <v>0</v>
       </c>
       <c r="K99" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L99" s="0">
-        <v>0.015550648462040852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.027074923697942281</v>
+        <v>0</v>
       </c>
       <c r="B100" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C100" s="0">
         <v>0</v>
       </c>
       <c r="D100" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E100" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0</v>
       </c>
       <c r="F100" s="0">
-        <v>0.0054579194411090446</v>
+        <v>0</v>
       </c>
       <c r="G100" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H100" s="0">
-        <v>0.022723399420553292</v>
+        <v>0</v>
       </c>
       <c r="I100" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0</v>
       </c>
       <c r="J100" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K100" s="0">
-        <v>3.7371134020618522</v>
+        <v>0</v>
       </c>
       <c r="L100" s="0">
-        <v>0.0046651945386122556</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
